--- a/BROMappings/Mapping en definitie BRO GLD.xlsx
+++ b/BROMappings/Mapping en definitie BRO GLD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/Meny_OS/trunk/BronDatamodel/BROMappings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{BE372826-5466-43B2-95C7-E0F7EC2978EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9818DFA3-33ED-4171-A15C-D0C028A1FD56}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{BE372826-5466-43B2-95C7-E0F7EC2978EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A71785D3-68AC-4E08-AE75-0B9067F9B8F9}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="269">
   <si>
     <t>Opmerking</t>
   </si>
@@ -732,9 +732,6 @@
     <t>Gravity</t>
   </si>
   <si>
-    <t>[m3 s−2 kg−1]</t>
-  </si>
-  <si>
     <t>isgmw</t>
   </si>
   <si>
@@ -829,6 +826,15 @@
   </si>
   <si>
     <t>[m+NAP]</t>
+  </si>
+  <si>
+    <t>[m3 s-2 kg-1]</t>
+  </si>
+  <si>
+    <t>GMN-BRO-ID</t>
+  </si>
+  <si>
+    <t>GMW-BRO-ID</t>
   </si>
 </sst>
 </file>
@@ -918,7 +924,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -945,6 +951,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -960,14 +967,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
-<file path=xl/persons/person0.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1363,10 +1362,10 @@
         <v>216</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="R2" s="13" t="s">
         <v>175</v>
@@ -1375,7 +1374,7 @@
         <v>219</v>
       </c>
       <c r="T2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -1423,10 +1422,10 @@
         <v>173</v>
       </c>
       <c r="P3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R3" s="13" t="s">
         <v>175</v>
@@ -1435,7 +1434,7 @@
         <v>219</v>
       </c>
       <c r="T3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -1483,10 +1482,10 @@
         <v>222</v>
       </c>
       <c r="P4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="R4" s="13" t="s">
         <v>175</v>
@@ -1495,7 +1494,7 @@
         <v>219</v>
       </c>
       <c r="T4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1542,10 +1541,10 @@
         <v>217</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="R5" s="12" t="s">
         <v>175</v>
@@ -1554,7 +1553,7 @@
         <v>219</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -1572,7 +1571,7 @@
         <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>215</v>
@@ -1696,13 +1695,13 @@
       </c>
       <c r="B9"/>
       <c r="C9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" t="s">
         <v>243</v>
       </c>
-      <c r="D9" t="s">
-        <v>244</v>
-      </c>
       <c r="E9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F9" t="s">
         <v>38</v>
@@ -1729,10 +1728,10 @@
         <v>216</v>
       </c>
       <c r="P9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>177</v>
@@ -1758,7 +1757,7 @@
         <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>34</v>
@@ -1782,13 +1781,13 @@
         <v>181</v>
       </c>
       <c r="R10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>219</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -1809,7 +1808,7 @@
         <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H11" t="s">
         <v>94</v>
@@ -1836,7 +1835,7 @@
         <v>183</v>
       </c>
       <c r="T11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1959,7 +1958,7 @@
         <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H14" t="s">
         <v>94</v>
@@ -2007,7 +2006,7 @@
         <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H15" t="s">
         <v>94</v>
@@ -2097,7 +2096,7 @@
         <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H17" t="s">
         <v>94</v>
@@ -2187,7 +2186,7 @@
         <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H19" t="s">
         <v>94</v>
@@ -2277,7 +2276,7 @@
         <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H21" t="s">
         <v>94</v>
@@ -2366,7 +2365,7 @@
         <v>68</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>94</v>
@@ -2408,7 +2407,7 @@
         <v>27</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>175</v>
@@ -2454,7 +2453,7 @@
         <v>27</v>
       </c>
       <c r="F25" t="s">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="G25" t="s">
         <v>215</v>
@@ -2475,10 +2474,10 @@
         <v>173</v>
       </c>
       <c r="P25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q25" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R25" t="s">
         <v>215</v>
@@ -2601,7 +2600,7 @@
         <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H28" t="s">
         <v>48</v>
@@ -2648,7 +2647,7 @@
         <v>43</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>48</v>
@@ -2786,7 +2785,7 @@
         <v>102</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>94</v>
@@ -2831,7 +2830,7 @@
         <v>113</v>
       </c>
       <c r="G33" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H33" t="s">
         <v>48</v>
@@ -2923,7 +2922,7 @@
         <v>115</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>34</v>
@@ -2947,7 +2946,7 @@
         <v>190</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -2962,7 +2961,7 @@
         <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F36" t="s">
         <v>124</v>
@@ -3341,7 +3340,7 @@
         <v>150</v>
       </c>
       <c r="G44" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H44" t="s">
         <v>94</v>
@@ -3385,7 +3384,7 @@
         <v>151</v>
       </c>
       <c r="G45" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>35</v>
@@ -3523,7 +3522,7 @@
         <v>160</v>
       </c>
       <c r="G48" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H48" t="s">
         <v>35</v>
@@ -3596,20 +3595,20 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B50"/>
       <c r="C50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D50" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50" t="s">
         <v>236</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>237</v>
-      </c>
-      <c r="F50" t="s">
-        <v>238</v>
       </c>
       <c r="G50" t="s">
         <v>196</v>
@@ -3636,7 +3635,7 @@
         <v>182</v>
       </c>
       <c r="T50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -3681,10 +3680,10 @@
         <v>217</v>
       </c>
       <c r="P51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R51" t="s">
         <v>183</v>
@@ -3889,13 +3888,13 @@
         <v>222</v>
       </c>
       <c r="P55" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>248</v>
+      </c>
+      <c r="R55" t="s">
         <v>249</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>249</v>
-      </c>
-      <c r="R55" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -3940,10 +3939,10 @@
         <v>222</v>
       </c>
       <c r="P56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R56" t="s">
         <v>182</v>
@@ -4056,7 +4055,7 @@
         <v>182</v>
       </c>
       <c r="T58" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.25">
@@ -4102,16 +4101,16 @@
         <v>222</v>
       </c>
       <c r="P59" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q59" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R59" t="s">
         <v>182</v>
       </c>
       <c r="T59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.25">
@@ -4214,8 +4213,8 @@
       <c r="Q61" t="s">
         <v>233</v>
       </c>
-      <c r="R61" t="s">
-        <v>234</v>
+      <c r="R61" s="14" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.25">
@@ -4374,7 +4373,7 @@
         <v>200</v>
       </c>
       <c r="T64" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.25">
